--- a/public/data/centres_couts.xlsx
+++ b/public/data/centres_couts.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mfadel\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pcazenp5\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560E78B6-D107-4510-8EEB-A8702A0EC581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10080"/>
+    <workbookView xWindow="-28920" yWindow="105" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -22,6 +23,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -29,9 +33,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="64">
   <si>
-    <t>Affectation générale</t>
-  </si>
-  <si>
     <t>Composante / Direction</t>
   </si>
   <si>
@@ -219,12 +220,15 @@
   </si>
   <si>
     <t>Population</t>
+  </si>
+  <si>
+    <t>affectation_generale</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -612,413 +616,413 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="F4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="G13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="E15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>23</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H15">
-    <sortState ref="A2:H15">
+  <autoFilter ref="A1:H15" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H15">
       <sortCondition ref="D2:D15"/>
       <sortCondition ref="E2:E15"/>
     </sortState>
